--- a/data_extactor/batch_10_fa/batch_0027_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0027_fa.xlsx
@@ -498,37 +498,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Core Inspector | Environmental Field Services Technician | Environmental Sampling Technician | Geological E-Logger | Geological Technician | Geoscience Technician | Geotechnician | Materials Technician | Physical Science Technician | Soils Technician</t>
+          <t>بازرس مغزه | تکنسین خدمات میدانی محیط‌زیست | تکنسین نمونه‌برداری محیط‌زیستی | متصدی نگارگیری الکترونیکی زمین‌شناسی | تکنسین زمین‌شناسی | تکنسین علوم زمین | تکنسین ژئوتکنیک | تکنسین مواد | تکنسین علوم فیزیکی | تکنسین خاک</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator | Autodesk AutoCAD | Clark Labs IDRISI Andes | Corel CorelDraw Graphics Suite | نرم‌افزار پایگاه داده | Dynamic Graphics EarthVision | ESRI ArcGIS software | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Geographic resources analysis support system GRASS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Golden Software Surfer | Halliburton ProMAX | IHS Petra | سیستم‌های مدیریت موجودی | Juniper Systems LandMark Mobile | Landmark Graphics GeoGraphix | Landmark SeisWorks | Leica Geosystems ERDAS IMAGINE | Martin D Adamiker's TruFlite | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Midland Valley 2DMove | Parallel Geoscience SPW | Petroleum Software Technologies | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Schlumberger GeoFrame | Seismic Micro-Technology KINGDOM | Surface III | Techsia Techlog | petroWEB Global Seismic Library</t>
+          <t>Adobe Illustrator | Autodesk AutoCAD | Clark Labs IDRISI Andes | Corel CorelDraw Graphics Suite | نرم‌افزار پایگاه داده | Dynamic Graphics EarthVision | نرم‌افزار ESRI ArcGIS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | سیستم پشتیبانی تحلیل منابع جغرافیایی GRASS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Golden Software Surfer | Halliburton ProMAX | IHS Petra | سیستم‌های مدیریت موجودی | Juniper Systems LandMark Mobile | Landmark Graphics GeoGraphix | Landmark SeisWorks | Leica Geosystems ERDAS IMAGINE | Martin D Adamiker's TruFlite | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Midland Valley 2DMove | Parallel Geoscience SPW | Petroleum Software Technologies | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Schlumberger GeoFrame | Seismic Micro-Technology KINGDOM | Surface III | Techsia Techlog | petroWEB Global Seismic Library</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | نوشتن | گوش دادن فعال | صحبت کردن</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | نگارش | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | شیمی | فیزیک | جغرافیا</t>
+          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | شیمی | فیزیک | جغرافیا</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شنیداری | مرتب‌سازی اطلاعات | دید نزدیک | بیان نوشتاری | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | حساسیت به مسئله | دید دور | توجه انتخابی | سرعت ادراکی | استدلال ریاضی</t>
+          <t>درک کتبی | درک شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | حساسیت به مسئله | بینایی دور | توجه انتخابی | سرعت ادراکی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق یا صحیح بودن | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف مشابه | تماس با دیگران | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | ارتباط با دیگران | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و متخصصان مهندسی و عملیات هوافضا | تکنسین‌ها و متخصصان کالیبراسیون | تکنسین‌های شیمی | مهندسان برق | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنسین‌ها و متخصصان مهندسی محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | نقشه‌برداران ژئودتیک | زمین‌شناسان، به استثنای هیدرولوژیست‌ها و جغرافی‌دانان | تکنسین‌های زمین‌گرمایی | تکنسین‌های هیدرولوژی | هیدرولوژیست‌ها | دانشمندان مواد | تکنسین‌ها و متخصصان مهندسی مکانیک | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | مهندسان نفت | دانشمندان و متخصصان سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و ترسیم</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های شیمی | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | نقشه‌برداران ژئودتیک | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های زمین‌گرمایی | تکنسین‌های هیدرولوژی | آب‌شناسان | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | مهندسان نفت | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,37 +555,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Field Hydrologic Technician | Hydrographer | Hydrologic Aide | Hydrologic Technician | Hydrology Technician | Stream Gauging Technician | Water Quality Technician | Water Resources Technician | Watershed Technician | Groundwater Technician</t>
+          <t>تکنسین میدانی آب‌شناسی | آب‌نگار | کمک‌یار آب‌شناسی | تکنسین آب‌شناسی | تکنسین آب‌شناسی | تکنسین آب‌سنجی رودخانه | تکنسین کیفیت آب | تکنسین منابع آب | تکنسین حوضه آبریز | تکنسین آب زیرزمینی</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Datasurge GEOPRO | Delft GeoSystems MStab | ESRI ArcGIS software | ESRI ArcInfo | ESRI ArcView | نرم‌افزار ایمیل | GEO-SLOPE SEEP/W | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mitre Software GSLOPE | Salix Applied Earthcare Erosion Draw | State Soil Geographic STATSGO Database</t>
+          <t>Adobe Acrobat | Datasurge GEOPRO | Delft GeoSystems MStab | نرم‌افزار ESRI ArcGIS | ESRI ArcInfo | ESRI ArcView | نرم‌افزار ایمیل | GEO-SLOPE SEEP/W | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Mitre Software GSLOPE | Salix Applied Earthcare Erosion Draw | پایگاه داده جغرافیایی خاک ایالتی STATSGO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | صحبت کردن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>جغرافیا | ریاضیات | شیمی | زبان انگلیسی | کامپیوتر و الکترونیک | مهندسی و فناوری | زیست‌شناسی | فیزیک</t>
+          <t>جغرافیا | ریاضیات | شیمی | زبان انگلیسی | رایانه و الکترونیک | مهندسی و فناوری | زیست‌شناسی | فیزیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند اندام | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض تمام شرایط آب و هوایی | فضای باز، زیر پوشش | در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه باز یا کار با تجهیزات | صرف زمان برای بالا رفتن از نردبان، داربست یا تیرک | در معرض مکان‌های مرتفع | صرف زمان برای زانو زدن، خم شدن، چمباتمه زدن یا خزیدن | صرف زمان برای حفظ یا بازیابی تعادل | بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تماس با دیگران | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | در معرض آلاینده‌ها | مکالمات تلفنی</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | فضای باز، زیر سقف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | در یک وسیله نقلیه روباز یا کار با تجهیزات | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | قرار گرفتن در معرض ارتفاعات بالا | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | صرف زمان برای حفظ یا بازیابی تعادل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دانشمندان جو و فضا | مهندسان عمران | دانشمندان حفاظت | تکنسین‌ها و متخصصان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | نقشه‌برداران ژئودتیک | جغرافی‌دانان | تکنسین‌ها و متخصصان سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به استثنای هیدرولوژیست‌ها و جغرافی‌دانان | هیدرولوژیست‌ها | اکولوژیست‌های صنعتی | دانشمندان و متخصصان سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و ترسیم | متخصصان منابع آب | مهندسان آب/فاضلاب</t>
+          <t>دانشمندان علوم جوی و فضایی | مهندسان عمران | دانشمندان حفاظت | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | نقشه‌برداران ژئودتیک | جغرافیدانان | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | آب‌شناسان | بوم‌شناسان صنعتی | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌کشی | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,37 +612,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auxiliary Operator | Equipment Operator | Licensed Nuclear Operator | Non-Licensed Nuclear Equipment Operator (NLO) | Non-Licensed Nuclear Plant Operator (NLO) | Nuclear Auxiliary Operator | Nuclear Equipment Operator (NEO) | Nuclear Plant Equipment Operator (NAPEO) | Operations Technician | Systems Operator</t>
+          <t>اپراتور کمکی | اپراتور تجهیزات | اپراتور هسته‌ای دارای پروانه | اپراتور تجهیزات هسته‌ای بدون پروانه (NLO) | اپراتور نیروگاه هسته‌ای بدون پروانه (NLO) | اپراتور تجهیزات جانبی هسته‌ای | اپراتور تجهیزات هسته‌ای (NEO) | اپراتور تجهیزات نیروگاه هسته‌ای (NAPEO) | تکنسین عملیات | اپراتور سیستم‌ها</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار ثبت داده | نرم‌افزار پایگاه داده | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Structured query language SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | VMWare ESX Server | VMware</t>
+          <t>نرم‌افزار ثبت داده‌ها | نرم‌افزار پایگاه داده | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | VMWare ESX Server | VMware</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نوشتن | صحبت کردن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | فیزیک | مهندسی و فناوری | آموزش و پرورش | شیمی | زبان انگلیسی | کامپیوتر و الکترونیک | ریاضیات | قانون و دولت</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | فیزیک | مهندسی و فناوری | آموزش و پرورش | شیمی | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | قانون و دولت</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال استقرایی | سرعت ادراکی | دید نزدیک | استدلال قیاسی | وضوح گفتار | بیان نوشتاری | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | دید دور | تشخیص رنگ بصری | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | اشتراک زمانی | زمان واکنش</t>
+          <t>حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | سرعت ادراکی | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | تشخیص رنگ بصری | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تقسیم توجه | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | در معرض تابش | ایمیل | محیط داخلی، دارای کنترل محیطی | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | محیط داخلی، بدون کنترل محیطی | تماس با دیگران | اهمیت تکرار وظایف مشابه | سلامت و ایمنی سایر کارگران | فراوانی تصمیم‌گیری | در معرض شرایط خطرناک | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در معرض دماهای بسیار گرم یا سرد | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در معرض شرایط نوری بسیار روشن یا نامناسب | در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | نزدیکی فیزیکی | در معرض تجهیزات خطرناک | در معرض فضای کاری تنگ، موقعیت‌های نامناسب | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تابش | صرف زمان برای استفاده از دستان خود برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | قرار گرفتن در معرض تابش | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، بدون کنترل شرایط محیطی | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط خطرناک | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | نزدیکی فیزیکی | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و متخصصان مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | تکنسین‌ها و متخصصان کالیبراسیون | مهندسان شیمی | اپراتورهای کارخانه و سیستم‌های شیمیایی | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تعمیرکاران برق و الکترونیک، نیروگاه، پست و رله | اپراتورهای کارخانه گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مهندسان هسته‌ای | تکنسین‌های نظارت هسته‌ای | اپراتورهای رآکتور نیروگاه هسته‌ای | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و اندازه‌گیرها | توزیع‌کنندگان و اعزام‌کنندگان نیرو | اپراتورهای نیروگاه | مهندسان ثابت و اپراتورهای دیگ بخار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | اپراتورهای کارخانه و سامانه‌های شیمیایی | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مهندسان هسته‌ای | تکنسین‌های نظارت هسته‌ای | اپراتورهای راکتور قدرت هسته‌ای | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -669,37 +669,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Health Physics Technician (HP Tech) | Nuclear Chemistry Technician | Radiation Control Technician (Radcon Technician) | Radiation Protection Specialist (RP Specialist) | Radiation Protection Technician (RPT) | Radiation Technician | Radiochemical Technician</t>
+          <t>تکنسین فیزیک بهداشت (HP Tech) | تکنسین شیمی هسته‌ای | تکنسین کنترل پرتو (Radcon) | کارشناس حفاظت در برابر پرتو (RP) | تکنسین حفاظت در برابر پرتو (RPT) | تکنسین پرتو | تکنسین رادیوشیمی</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AVEVA InTouch HMI | نرم‌افزار اتصال | Gamma waste assay system GWAS | Google Compute Engine (GCE) | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Oracle Java | RESRAD | Radiological assessment display and control system RADACS | Structured query language SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA</t>
+          <t>AVEVA InTouch HMI | نرم‌افزار اتصال | Gamma waste assay system GWAS | Google Compute Engine (GCE) | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Oracle Java | RESRAD | Radiological assessment display and control system RADACS | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | صحبت کردن | ریاضیات | علوم | استراتژی‌های یادگیری | نوشتن | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | ریاضیات | علوم | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ریاضیات | فیزیک | ایمنی و امنیت عمومی | شیمی | زبان انگلیسی | کامپیوتر و الکترونیک</t>
+          <t>ریاضیات | فیزیک | ایمنی و امنیت عمومی | شیمی | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شنیداری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک نوشتاری | بیان نوشتاری | مرتب‌سازی اطلاعات | توجه انتخابی | سرعت ادراکی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | خلاقیت | ثبات دست و بازو | اشتراک زمانی | تشخیص رنگ بصری | دید دور</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | توجه انتخابی | سرعت ادراکی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | اصالت | ثبات دست و بازو | تقسیم توجه | تشخیص رنگ بصری | بینایی دور</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | در معرض تابش | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | سلامت و ایمنی سایر کارگران | تماس با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فراوانی تصمیم‌گیری | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا حفاظت در برابر تابش | محیط داخلی، بدون کنترل محیطی | نزدیکی فیزیکی | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف مشابه | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نتایج کاری و خروجی‌های سایر کارگران | فشار زمانی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | قرار گرفتن در معرض تابش | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | محیط داخلی، بدون کنترل شرایط محیطی | نزدیکی فیزیکی | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و متخصصان کالیبراسیون | اپراتورهای کارخانه و سیستم‌های شیمیایی | تکنسین‌های شیمی | شیمیدانان | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنسین‌ها و متخصصان مهندسی محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | کارگران حذف مواد خطرناک | مهندسان بهداشت و ایمنی، به استثنای مهندسان و بازرسان ایمنی معدن | تکنسین‌های آزمایشگاه پزشکی و بالینی | متخصصان آزمایشگاه پزشکی و بالینی | تکنسین‌ها و متخصصان مهندسی نانوتکنولوژی | متخصصان تست‌های غیرمخرب | مهندسان هسته‌ای | تکنسین‌های پزشکی هسته‌ای | اپراتورهای رآکتور نیروگاه هسته‌ای | تکنسین‌های هسته‌ای | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | اپراتورهای کارخانه و سیستم‌های تصفیه آب و فاضلاب</t>
+          <t>تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای کارخانه و سامانه‌های شیمیایی | تکنسین‌های شیمی | شیمی‌دانان | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | کارگران حذف مواد خطرناک | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | متخصصان تست غیرمخرب | مهندسان هسته‌ای | تکنولوژیست‌های پزشکی هسته‌ای | اپراتورهای راکتور قدرت هسته‌ای | تکنسین‌های هسته‌ای | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -726,37 +726,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clinical Research Assistant | Graduate Assistant | Graduate Research Assistant | Research Aide | Research Assistant | Research Associate | Research Technician | Social Research Assistant</t>
+          <t>دستیار پژوهش بالینی | دستیار فارغ‌التحصیل | دستیار پژوهشی فارغ‌التحصیل | کمک‌یار پژوهش | دستیار پژوهشی | دستیار پژوهشی | تکنسین تحقیقاتی | دستیار پژوهش اجتماعی</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adobe Illustrator | Adobe InDesign | Appletree | C++ | نرم‌افزار پایگاه داده | ESRI ArcGIS software | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار گرافیکی | IBM SPSS Statistics | JavaScript | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Word | پایگاه‌های داده کتابخانه آنلاین | Oracle Java | Perl | Python | Qualtrics Insight | R | REDCap Research Electronic Data Capture | SAS | StataCorp Stata | نرم‌افزار آماری | Structured query language SQL | Tableau | The MathWorks MATLAB | نرم‌افزار توسعه ویدئو | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Illustrator | Adobe InDesign | Appletree | C++ | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار گرافیکی | IBM SPSS Statistics | JavaScript | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Word | پایگاه‌های داده کتابخانه آنلاین | Oracle Java | Perl | Python | Qualtrics Insight | R | REDCap Research Electronic Data Capture | SAS | StataCorp Stata | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | Tableau | The MathWorks MATLAB | نرم‌افزار توسعه ویدئو | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتن | تفکر انتقادی | صحبت کردن | علوم | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | علوم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | کامپیوتر و الکترونیک | اداری | ریاضیات | خدمات مشتری و شخصی</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | اداری | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | مرتب‌سازی اطلاعات | استدلال قیاسی | دید نزدیک | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | استدلال ریاضی | حساسیت به مسئله | خلاقیت | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | استدلال ریاضی | حساسیت به مسئله | اصالت | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>صرف زمان برای نشستن | ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف مشابه | تماس با دیگران</t>
+          <t>صرف زمان برای نشستن | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت تکرار وظایف یکسان | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | متخصصان آمار زیستی | مدیران داده‌های بالینی | هماهنگ‌کنندگان تحقیقات بالینی | دانشمندان داده | مدیران آموزش، پس از متوسطه | معلمان آموزش، پس از متوسطه | منشی‌های اجرایی و دستیاران اداری اجرایی | متخصصان انفورماتیک سلامت | متخصصان فناوری اطلاعات سلامت و ثبت‌کنندگان پزشکی | هماهنگ‌کنندگان آموزشی | مصاحبه‌کنندگان، به استثنای واجد شرایط بودن و وام | تحلیل‌گران مدیریت | منشی‌ها و دستیاران اداری، به استثنای حقوقی، پزشکی و اجرایی | جامعه‌شناسان | دستیاران آماری | آماردانان | محققان نظرسنجی | دستیاران آموزشی، پس از متوسطه | نویسندگان فنی</t>
+          <t>تکنسین‌های بیوانفورماتیک | آمارشناسان زیستی | مدیران داده‌های بالینی | هماهنگ‌کنندگان تحقیقات بالینی | دانشمندان داده | مدیران آموزشی، پس از متوسطه | مدرسان علوم تربیتی، آموزش عالی | منشی‌های اجرایی و دستیاران اداری اجرایی | متخصصان انفورماتیک سلامت | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | هماهنگ‌کنندگان آموزشی | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | تحلیل‌گران مدیریت | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | جامعه‌شناسان | دستیاران آماری | آمارشناسان | پژوهشگران نظرسنجی | دستیاران آموزشی، مقطع پس از متوسطه | نویسندگان فنی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -783,37 +783,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biological Science Aide | Forest Technician | Forestry Aide | Forestry Technician (Forestry Tech) | Resource Technician | Timber Appraiser</t>
+          <t>کمک‌یار علوم زیستی | تکنسین جنگل | کمک‌یار جنگلداری | تکنسین جنگلداری (Forestry Tech) | تکنسین منابع | ارزیاب چوب و الوار</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Allegro Landmark | Assisi Compiler | Assisi Forest | Assisi Inventory | Atterbury Consultants SuperAce | Autodesk AutoCAD LT | Ben Meadows Yeoman Expedition | نرم‌افزار گرافیک کامپیوتری | Corel Presentation | نرم‌افزار پایگاه داده | ESRI ArcGIS software | ESRI ArcView | Facebook | نرم‌افزار مدل‌سازی رفتار آتش | Forest EcoSurvey | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | HARVEST | Haglof Sweden AB TCruise Forest Inventory | JRP Consulting Plant Wizard | JRP Consulting Survey Wizard | LJI Technologies Lumberjack | Leica Geosystems ERDAS IMAGINE | LoggerPC software | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | PhoenixPRO Forest Activity Tracking | نرم‌افزار فتوگرامتری | نرم‌افزار سنجش از دور | RockWare ArcMap | Traverse PC | USDA Forest Vegetation Simulator FVS | نرم‌افزار مرورگر وب</t>
+          <t>Allegro Landmark | Assisi Compiler | Assisi Forest | Assisi Inventory | Atterbury Consultants SuperAce | Autodesk AutoCAD LT | Ben Meadows Yeoman Expedition | نرم‌افزار گرافیک کامپیوتری | Corel Presentation | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | ESRI ArcView | Facebook | نرم‌افزار مدل‌سازی رفتار آتش | Forest EcoSurvey | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | HARVEST | Haglof Sweden AB TCruise Forest Inventory | JRP Consulting Plant Wizard | JRP Consulting Survey Wizard | LJI Technologies Lumberjack | Leica Geosystems ERDAS IMAGINE | LoggerPC software | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | PhoenixPRO Forest Activity Tracking | نرم‌افزار فتوگرامتری | نرم‌افزار سنجش از دور | RockWare ArcMap | Traverse PC | USDA Forest Vegetation Simulator FVS | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | صحبت کردن | نظارت | استراتژی‌های یادگیری | یادگیری فعال | نوشتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | جغرافیا | مدیریت و اداره | ریاضیات | آموزش و پرورش | زیست‌شناسی | مکانیک | کامپیوتر و الکترونیک | پرسنل و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | جغرافیا | مدیریت و اداره | ریاضیات | آموزش و پرورش | زیست‌شناسی | مکانیک | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | درک شنیداری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک نوشتاری | دید دور | دید نزدیک | تجسم | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | بیان نوشتاری | خلاقیت | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | هماهنگی چند اندام | دقت کنترل | مهارت انگشتان</t>
+          <t>ترتیب‌دهی اطلاعات | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بینایی دور | بینایی نزدیک | تجسم | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | بیان کتبی | اصالت | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارگران | محیط داخلی، دارای کنترل محیطی | اهمیت دقیق یا صحیح بودن | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دستان خود برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | در معرض دماهای بسیار گرم یا سرد | در معرض سوختگی‌های جزئی، بریدگی‌ها، گزش‌ها یا نیش‌ها | نامه‌ها و یادداشت‌های کتبی | نتایج کاری و خروجی‌های سایر کارگران | اهمیت تکرار وظایف مشابه | پیامد خطا | صرف زمان برای ایستادن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | نزدیکی فیزیکی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | نامه‌ها و یادداشت‌های کتبی | پیامدهای کاری و نتایج سایر کارکنان | اهمیت تکرار وظایف یکسان | پیامد خطا | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و متخصصان مهندسی محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان رده اول کارگران کشاورزی، ماهیگیری و جنگلداری | سرپرستان رده اول کارگران محوطه‌سازی، خدمات چمن و نگهداری زمین | بازرسان آتش‌سوزی جنگل و متخصصان پیشگیری | کارگران جنگل و حفاظت | جنگل‌بانان | تکنسین‌های هیدرولوژی | اکولوژیست‌های صنعتی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های کشاورزی دقیق | مدیران مراتع | دانشمندان خاک و گیاه | متخصصان منابع آب</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | کارگران جنگل و حفاظت | جنگل‌بانان | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های کشاورزی دقیق | مدیران مراتع | دانشمندان خاک و گیاه | متخصصان منابع آب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -840,37 +840,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CSI (Crime Scene Investigator) | Crime Lab Analyst (Crime Laboratory Analyst) | Crime Scene Analyst (CSA) | Crime Scene Technician (Crime Scene Tech) | Criminalist | Evidence Technician (Evidence Tech) | Forensic Science Examiner | Forensic Scientist | Forensic Specialist | Latent Print Examiner</t>
+          <t>CSI (بازرس صحنه جرم) | تحلیلگر آزمایشگاه جرم‌شناسی | تحلیل‌گر صحنه جرم (CSA) | تکنسین صحنه جرم (Crime Scene Tech) | جرم‌شناس | تکنسین شواهد | کارشناس علوم جنایی | دانشمند علوم جنایی | متخصص پزشکی قانونی | کارشناس اثر انگشت پنهان</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | Automated Biometric Identification System ABIS | Combined DNA Index System CODIS | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel WordPerfect Office Suite | DM2 Bills of Lading | DataWorks Plus Digital CrimeScene | DesignWare 3D EyeWitness | Eos Systems PhotoModeler | نرم‌افزار گرافیکی | Guidance Software EnCase Enterprise | IBM Notes | نرم‌افزار بهبود تصویر | Integrated Automated Fingerprint Identification System IAFIS | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Mideo Systems EZDoc Plus | Midwest Information Systems PAX-it | پایگاه داده National Crime Information Center (NCIC) | National Integrated Ballistics Information Network NIBIN | SmartDraw Legal | The CAD Zone The Crime Zone | Trancite Logic Systems ScenePD | Visual Statement Vista FX3 CSI | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Photoshop | Automated Biometric Identification System ABIS | Combined DNA Index System CODIS | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel WordPerfect Office Suite | DM2 Bills of Lading | DataWorks Plus Digital CrimeScene | DesignWare 3D EyeWitness | Eos Systems PhotoModeler | نرم‌افزار گرافیکی | Guidance Software EnCase Enterprise | IBM Notes | نرم‌افزار بهبود تصویر | سیستم یکپارچه خودکار شناسایی اثر انگشت IAFIS | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | Mideo Systems EZDoc Plus | Midwest Information Systems PAX-it | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی یکپارچه اطلاعات بالستیک NIBIN | SmartDraw Legal | The CAD Zone The Crime Zone | Trancite Logic Systems ScenePD | Visual Statement Vista FX3 CSI | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | صحبت کردن | نوشتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | علوم | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>قانون و دولت | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | کامپیوتر و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره | شیمی | اداری | زیست‌شناسی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره | شیمی | اداری | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | انعطاف‌پذیری بستار | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید دور | تشخیص گفتار | وضوح گفتار | تشخیص رنگ بصری | سرعت ادراکی | روانی ایده‌ها | سرعت بستار | تجسم | ثبات دست و بازو | توجه انتخابی</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | انعطاف‌پذیری بستار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی دور | تشخیص گفتار | وضوح گفتار | تشخیص رنگ بصری | سرعت ادراکی | روانی ایده‌ها | سرعت بستار | تجسم | ثبات دست و بازو | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | فراوانی تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | در معرض آلاینده‌ها | نزدیکی فیزیکی | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | آزادی در تصمیم‌گیری | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | در معرض دماهای بسیار گرم یا سرد | فضای باز، زیر پوشش | در معرض شرایط نوری بسیار روشن یا نامناسب</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض آلاینده‌ها | نزدیکی فیزیکی | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | آزادی در تصمیم‌گیری | پیامد خطا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، زیر سقف | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیولوژیکی | بازپرسان جنایی | متخصصان سیتوژنتیک | دانشمندان داده | کارآگاهان و بازپرسان جنایی | تحلیل‌گران پزشکی قانونی دیجیتال | بازرسان انطباق زیست‌محیطی | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | بازرسان و تحلیل‌گران کلاهبرداری | تکنسین‌های بافت‌شناسی | تحلیل‌گران اطلاعات | تکنسین‌های آزمایشگاه پزشکی و بالینی | متخصصان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تکنسین‌های نظارت هسته‌ای | تست‌کنندگان نفوذ | خون‌گیرها | پزشکان، آسیب‌شناسان | افسران شناسایی و سوابق پلیس | کارآگاهان و بازپرسان خصوصی</t>
+          <t>تکنسین‌های زیستی | بازرسان مرگ | تکنولوژیست‌های سیتوژنتیک | دانشمندان داده | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌شناسی دیجیتال | بازرسان انطباق زیست‌محیطی | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | بازرسان، محققان و تحلیلگران کلاهبرداری | تکنیسین‌های هیستولوژی | تحلیلگران اطلاعاتی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تکنسین‌های نظارت هسته‌ای | کارشناسان آزمون نفوذ | فلبوتومیست‌ها | پزشکان، آسیب‌شناسان | افسران شناسایی و سوابق پلیس | کارآگاهان و بازرسان خصوصی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Analytical Technician | Field Technician | Laboratory Assistant | Laboratory Technician | Research Assistant | Research Technician | Sample Technician | Science Technician | Testing Technician | Lab Aide</t>
+          <t>تکنسین تحلیل آزمایشگاهی | تکنسین میدانی | دستیار آزمایشگاه | تکنسین آزمایشگاه | دستیار پژوهشی | تکنسین تحقیقاتی | تکنسین نمونه‌برداری | تکنسین علوم | تکنسین آزمون | کمک‌یار آزمایشگاه</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | صحبت کردن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>شیمی | زیست‌شناسی | ریاضیات | زبان انگلیسی | کامپیوتر و الکترونیک | مهندسی و فناوری | فیزیک</t>
+          <t>شیمی | زیست‌شناسی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مهندسی و فناوری | فیزیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند اندام | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | در معرض شرایط خطرناک | صرف زمان برای ایستادن | صرف زمان برای استفاده از دستان خود برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | اهمیت تکرار وظایف مشابه</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیولوژیکی | تکنسین‌های شیمی | تکنسین‌های کشاورزی | تکنسین‌های علوم غذایی | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | تکنسین‌های هسته‌ای | تکنسین‌های نظارت هسته‌ای | تکنسین‌های علوم قانونی | تکنسین‌های جنگل و حفاظت | دستیاران تحقیقات علوم اجتماعی | تحلیل‌گران کنترل کیفیت | تکنسین‌های سنجش از دور | تکنسین‌های کشاورزی دقیق | تکنسین‌های بهداشت و ایمنی شغلی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌ها و متخصصان کالیبراسیون | زیست‌شناسان | شیمیدانان</t>
+          <t>تکنسین‌های زیستی | تکنسین‌های شیمی | تکنسین‌های کشاورزی | تکنسین‌های علوم غذایی | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | تکنسین‌های هسته‌ای | تکنسین‌های نظارت هسته‌ای | تکنسین‌های علوم قانونی | تکنسین‌های جنگل و حفاظت | دستیاران تحقیقات علوم اجتماعی | تحلیل‌گران کنترل کیفیت | تکنسین‌های سنجش از دور | تکنسین‌های کشاورزی دقیق | تکنسین‌های بهداشت و ایمنی شغلی | متخصصان بهداشت و ایمنی شغلی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | زیست‌شناسان | شیمی‌دانان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -954,37 +954,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lab Analyst | Lab Technician (Lab Tech) | Laboratory Analyst | Microbiology Lab Analyst | QA Auditor (Quality Assurance Auditor) | QA Lab Tech (Quality Assurance Lab Technician) | QA Tech (Quality Assurance Technician) | Quality Control Analyst (QC Analyst) | Quality Control Lab Technician (QC Lab Tech) | Quality Control Technician (QC Tech)</t>
+          <t>تحلیل‌گر آزمایشگاه | تکنسین آزمایشگاه (Lab Tech) | تحلیل‌گر آزمایشگاه | تحلیل‌گر آزمایشگاه میکروب‌شناسی | حسابرس تضمین کیفیت | تکنسین آزمایشگاه تضمین کیفیت (QA) | تکنسین تضمین کیفیت (QA Tech) | تحلیل‌گر کنترل کیفیت (QC) | تکنسین آزمایشگاه کنترل کیفیت (QC Lab Tech) | تکنسین کنترل کیفیت</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Atlassian JIRA | Borland SilkTest | C | پروفایل‌کننده‌های کد | نرم‌افزار پایگاه داده | Eko | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | Hewlett Packard LoadRunner | Hewlett Packard QuickTest Professional | زبان نشانه‌گذاری ابرمتنی HTML | IBM Notes | IBM Rational Functional Tester | IBM Rational Robot | JavaScript | LabWare LIMS | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Micro Focus TestPartner | Microsoft ASP.NET | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Studio Test Professional | Microsoft Windows | Microsoft Word | Minitab | National Instruments LabVIEW | Parasoft SOAtest | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Selenium | SmartBear Software AutomatedQA TestComplete | SmugMug Flickr | Sparta Systems TrackWise | Structured query language SQL | نرم‌افزار تست خودکار | The MathWorks MATLAB | Watir | dBASE</t>
+          <t>Adobe Acrobat | Atlassian JIRA | Borland SilkTest | C | پروفایل‌کننده‌های کد | نرم‌افزار پایگاه داده | Eko | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | Hewlett Packard LoadRunner | Hewlett Packard QuickTest Professional | زبان نشانه‌گذاری ابرمتن HTML | IBM Notes | IBM Rational Functional Tester | IBM Rational Robot | JavaScript | LabWare LIMS | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Micro Focus TestPartner | Microsoft ASP.NET | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Studio Test Professional | Microsoft Windows | Microsoft Word | Minitab | National Instruments LabVIEW | Parasoft SOAtest | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Selenium | SmartBear Software AutomatedQA TestComplete | SmugMug Flickr | Sparta Systems TrackWise | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار تست خودکار | The MathWorks MATLAB | Watir | dBASE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | نوشتن | صحبت کردن | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ریاضیات | تولید و پردازش | شیمی | زبان انگلیسی | اداری | کامپیوتر و الکترونیک</t>
+          <t>ریاضیات | تولید و فرآوری | شیمی | زبان انگلیسی | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک نوشتاری | درک شنیداری | بیان نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید دور | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | مرتب‌سازی اطلاعات | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | ثبات دست و بازو</t>
+          <t>بینایی نزدیک | درک کتبی | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی دور | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | در معرض آلاینده‌ها | صرف زمان برای استفاده از دستان خود برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | در معرض شرایط خطرناک | اهمیت تکرار وظایف مشابه | آزادی در تصمیم‌گیری | تماس با دیگران | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض شرایط خطرناک | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و متخصصان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و متخصصان کالیبراسیون | تکنسین‌های شیمی | شیمیدانان | تکنسین‌های علوم غذایی | مهندسان بهداشت و ایمنی، به استثنای مهندسان و بازرسان ایمنی معدن | هیستوتکنولوژیست‌ها | تکنسین‌ها و متخصصان مهندسی صنایع | مهندسان صنایع | بازرسان، تست‌کنندگان، مرتب‌کنندگان، نمونه‌گیرها و وزن‌کنندگان | تکنسین‌ها و متخصصان مهندسی مکانیک | تکنسین‌های آزمایشگاه پزشکی و بالینی | متخصصان آزمایشگاه پزشکی و بالینی | تکنسین‌ها و متخصصان مهندسی نانوتکنولوژی | تست‌کنندگان نفوذ | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های شیمی | شیمی‌دانان | تکنسین‌های علوم غذایی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | هیستوتکنولوژیست‌ها | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | تکنسین‌ها و کارشناسان مهندسی مکانیک | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | کارشناسان آزمون نفوذ | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1011,37 +1011,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Digital Cartographic Technician | Geospatial Extractor | Meteorologist Liaison | Research Associate</t>
+          <t>تکنسین نقشه‌نگاری دیجیتال | استخراج‌کننده داده مکانی | رابط هواشناسی | دستیار پژوهشی</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AJAX | نرم‌افزار Adobe Creative Cloud | Adobe Photoshop | نقشه‌های هوانوردی | Agisoft Metashape | Airdata | Amazon Elastic Compute Cloud EC2 | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Applied Imagery Quick Terrain Modeler | ArduPilot Mission Planner | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | BAE Systems SOCET SET | Bentley MicroStation | C | C# | C++ | نرم‌افزار کالیبراسیون | برگه‌های سبک آبشاری CSS | CloudCompare | Common MASINT Exploitation Tool COMET | Corpscon | نرم‌افزار دیباگ | Definiens Developer | ESRI ArcCatalog | ESRI ArcGIS software | ESRI ArcMap | ESRI ArcView 3D Analyst | ESRI Site Scan for ArcGIS | FLIR Thermal Studio Suite | نرم‌افزار نقشه‌برداری LIDAR و پهپاد GeoCue | GeoCue PointVue LE | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Git | GitHub | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Google Analytics | زبان نشانه‌گذاری ابرمتنی HTML | پیش‌پردازنده ابرمتنی PHP | ITT Visual Information Solutions ENVI | زبان تعریف رابط IDL | JavaScript | Kitty Hawk | LP360 | سیستم تشخیص و فاصله‌یابی لیزری LIDAR | Leica Geosystems ERDAS IMAGINE | Linux | Litchi | Magellan Firmware | Mathsoft Mathcad | Microsoft .NET Framework | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | Microsoft Image Composite Editor | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | MySQL | OpenDroneMap | Opticks | Oracle Database | Oracle Java | Perl | Pix4D Pix4Dmapper | Python | QGIS | R | React | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | ServiceNow | اسکریپت پوسته | Splunk Enterprise | Structure query language SQL | Structured query language SQL | Terrasolid TerraScan | The MathWorks MATLAB | UNIX | UNIX Shell | UgCS | VMware | Verilog | نرم‌افزار مرورگر وب | jQuery</t>
+          <t>AJAX | نرم‌افزار Adobe Creative Cloud | Adobe Photoshop | نقشه‌های هوانوردی | Agisoft Metashape | Airdata | Amazon Elastic Compute Cloud EC2 | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Applied Imagery Quick Terrain Modeler | ArduPilot Mission Planner | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | BAE Systems SOCET SET | Bentley MicroStation | C | C# | C++ | نرم‌افزار کالیبراسیون | برگه‌های سبک آبشاری CSS | CloudCompare | Common MASINT Exploitation Tool COMET | Corpscon | نرم‌افزار عیب‌یابی | Definiens Developer | ESRI ArcCatalog | نرم‌افزار ESRI ArcGIS | ESRI ArcMap | ESRI ArcView 3D Analyst | ESRI Site Scan for ArcGIS | FLIR Thermal Studio Suite | نرم‌افزار نقشه‌برداری LIDAR و پهپاد GeoCue | GeoCue PointVue LE | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Git | GitHub | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Google Analytics | زبان نشانه‌گذاری ابرمتن HTML | Hypertext preprocessor PHP | ITT Visual Information Solutions ENVI | زبان تعریف رابط IDL | JavaScript | Kitty Hawk | LP360 | سیستم تصویربرداری لیزری و ردیابی LIDAR | Leica Geosystems ERDAS IMAGINE | Linux | Litchi | Magellan Firmware | Mathsoft Mathcad | Microsoft .NET Framework | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | Microsoft Image Composite Editor | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft SQL Server | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | MySQL | OpenDroneMap | Opticks | Oracle Database | Oracle Java | Perl | Pix4D Pix4Dmapper | Python | QGIS | R | React | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | ServiceNow | Shell script | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | زبان پرس‌وجوی ساختاریافته SQL | Terrasolid TerraScan | The MathWorks MATLAB | UNIX | UNIX Shell | UgCS | VMware | Verilog | نرم‌افزار مرورگر وب | jQuery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | صحبت کردن | ریاضیات | گوش دادن فعال | نظارت | نوشتن | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات | گوش دادن فعال | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | کامپیوتر و الکترونیک | ریاضیات | خدمات مشتری و شخصی | مهندسی و فناوری | تولید و پردازش | زبان انگلیسی</t>
+          <t>جغرافیا | رایانه و الکترونیک | ریاضیات | خدمات مشتری و شخصی | مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | بیان شفاهی | دید نزدیک | استدلال استقرایی | درک شنیداری | بیان نوشتاری | وضوح گفتار | درک نوشتاری | انعطاف‌پذیری بستار | تشخیص گفتار | روانی ایده‌ها | خلاقیت | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | توجه انتخابی | سرعت ادراکی | توانایی عددی</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان شفاهی | بینایی نزدیک | استدلال استقرایی | درک شفاهی | بیان کتبی | وضوح گفتار | درک کتبی | انعطاف‌پذیری بستار | تشخیص گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | توجه انتخابی | سرعت ادراکی | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای کنترل محیطی | ایمیل | اهمیت دقیق یا صحیح بودن | بحث‌های حضوری با افراد و درون تیم‌ها | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تماس با دیگران | اهمیت تکرار وظایف مشابه | فشار زمانی | مکالمات تلفنی | صرف زمان برای استفاده از دستان خود برای جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | فشار زمانی | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و متخصصان مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های اویونیک | تکنسین‌ها و متخصصان کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | نقشه‌برداران و فتوگرامتریست‌ها | تکنسین‌ها و متخصصان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنسین‌ها و متخصصان الکترومکانیک و مکاترونیک | نقشه‌برداران ژئودتیک | تکنسین‌ها و متخصصان سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های کشاورزی دقیق | متخصصان دستگاه شناسایی فرکانس رادیویی | دانشمندان و متخصصان سنجش از دور | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | تکنسین‌های نقشه‌برداری و ترسیم | نقشه‌برداران</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | نقشه‌برداران و فتوگرامتریست‌ها | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | نقشه‌برداران ژئودتیک | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های کشاورزی دقیق | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | دانشمندان و فناوران سنجش از دور | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | تکنسین‌های نقشه‌برداری و نقشه‌کشی | نقشه‌برداران</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0027_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0027_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | نگارش | شنیدن فعال | سخن گفتن</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | نگارش | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | مرتب‌سازی اطلاعات | دید نزدیک | بیان کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | حساسیت به مسئله | دید دور | توجه انتخابی | سرعت ادراک | استدلال ریاضی</t>
+          <t>درک کتبی | درک شفاهی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بستار | حساسیت به مسئله | بینایی دور | توجه انتخابی | سرعت ادراکی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی و عملیات هوافضا | کاردان‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های شیمی | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کاردان‌ها و تکنسین‌های مهندسی محیط‌زیست | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | نقشه‌برداران ژئودتیک | متخصصان علوم زمین به‌جز آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های زمین‌گرمایی | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | دانشمندان علوم مواد | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان معدن و زمین‌شناسی ازجمله مهندسان ایمنی معدن | مهندسان نفت | دانشمندان و کارشناسان فناوری سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های شیمی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های مهندسی محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | مهندسان نقشه‌برداری ژئودزی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | مهندسان نفت | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | پایداری دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل | هماهنگی اندام‌ها | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دانشمندان علوم جوی و فضا | مهندسان عمران | دانشمندان حفاظت منابع طبیعی | کاردان‌ها و تکنسین‌های مهندسی محیط‌زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | کارشناسان و دانشمندان علوم محیط‌زیست ازجمله بهداشت محیط | نقشه‌برداران ژئودتیک | جغرافیدانان | کاردان‌ها و تکنسین‌های سیستم اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | متخصصان علوم زمین به‌جز آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | اکولوژیست‌های صنعتی | دانشمندان و کارشناسان فناوری سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌کشی | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
+          <t>دانشمندان و کارشناسان علوم جوی و فضا | مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان نقشه‌برداری ژئودزی | جغرافیدانان | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مکانیک | فیزیک | مهندسی و فناوری | آموزش و تدریس | شیمی | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | حقوق و مقررات دولتی</t>
+          <t>ایمنی و امنیت عمومی | مکانیک | فیزیک | مهندسی و فناوری | آموزش و پرورش | شیمی | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | قانون و دولت</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | سرعت ادراک | دید نزدیک | استدلال قیاسی | وضوح گفتار | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | دید دور | تمایز رنگ‌ها | دقت کنترل | چابکی انگشتان | چابکی دستی | پایداری دست و بازو | تقسیم توجه | زمان واکنش</t>
+          <t>حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | استدلال استقرایی | سرعت ادراکی | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | بینایی دور | تشخیص رنگ بصری | دقت کنترل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | تقسیم توجه | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | کاردان‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | اپراتورهای کارخانه و سیستم‌های فرآیندی شیمیایی | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی نیروگاه، پست برق و رله | اپراتورهای پالایشگاه و تأسیسات گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مهندسان هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | اپراتورهای رآکتور هسته‌ای | اپراتورهای پمپ‌خانه نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | توزیع‌کنندگان و دیسپاچرهای برق | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ بخار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مهندسان هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | اپراتورهای رآکتور نیروگاه هسته‌ای | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | ریاضیات | علوم | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | ریاضیات | علوم | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | توجه انتخابی | سرعت ادراک | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | مهارت محاسبات عددی | استدلال ریاضی | ابتکار و اصالت | پایداری دست و بازو | تقسیم توجه | تمایز رنگ‌ها | دید دور</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | توجه انتخابی | سرعت ادراکی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی عددی | استدلال ریاضی | اصالت | ثبات دست و بازو | تقسیم توجه | تشخیص رنگ بصری | بینایی دور</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های کالیبراسیون | اپراتورهای کارخانه و سیستم‌های فرآیندی شیمیایی | تکنسین‌های شیمی | شیمیدانان | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کاردان‌ها و تکنسین‌های مهندسی محیط‌زیست | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | کارگران جمع‌آوری و امحای پسماندهای خطرناک | مهندسان ایمنی و بهداشت به‌جز مهندسان و بازرسان ایمنی معدن | کاردان‌ها و تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان آزمایشگاه‌های تشخیص پزشکی و بالینی | کاردان‌ها و تکنسین‌های مهندسی نانوفناوری | متخصصان آزمون‌های غیرمخرب (NDT) | مهندسان هسته‌ای | کارشناسان فناوری پزشکی هسته‌ای | اپراتورهای رآکتور هسته‌ای | تکنسین‌های هسته‌ای | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | اپراتورهای تصفیه‌خانه و سیستم‌های تصفیه آب و فاضلاب</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تکنسین‌های شیمی | شیمی‌دانان | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های مهندسی محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارگران امحا و پاک‌سازی مواد خطرناک | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | متخصصان آزمون‌های غیرمخرب NDT | مهندسان هسته‌ای | کارشناسان و تکنسین‌های پزشکی هسته‌ای | اپراتورهای رآکتور نیروگاه هسته‌ای | تکنسین‌های هسته‌ای | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | علوم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | علوم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | رایانه و الکترونیک | اداری | ریاضیات | خدمات مشتریان و خدمات فردی</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | اداری | ریاضیات | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی | دید نزدیک | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | استدلال ریاضی | حساسیت به مسئله | ابتکار و اصالت | روانی و سیالی ایده‌ها | مهارت محاسبات عددی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بینایی نزدیک | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | استدلال ریاضی | حساسیت به مسئله | اصالت | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | مدیران داده‌های بالینی | هماهنگ‌کنندگان پژوهش‌های بالینی | دانشمندان داده | مدیران آموزش عالی | مدرسان دانشگاه و آموزش عالی | مسئولان دفتر و دستیاران اجرایی مدیریت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی آموزشی | مصاحبه‌گران به‌جز مصاحبه‌گران اعتبارسنجی و وام | تحلیل‌گران مدیریت و بهبود فرایند | مسئولان دفتر و کارمندان امور دفتری به‌جز حقوقی، پزشکی و اجرایی | جامعه‌شناسان | دستیاران و کاردان‌های آمار | کارشناسان آمار | پژوهشگران و تحلیل‌گران نظرسنجی | دستیاران آموزشی دانشگاه و آموزش عالی | کارشناسان نگارش متون فنی</t>
+          <t>تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | مدیران داده‌های بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | دانشمندان داده | مدیران آموزش عالی | مدرسان علوم تربیتی و آموزش در دانشگاه‌ها و مراکز آموزش عالی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متخصصان انفورماتیک سلامت | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | کارشناسان تحلیل مدیریت و روش‌ها | منشی‌ها و دستیاران اداری عمومی | جامعه‌شناسان | دستیاران و تکنسین‌های آمار | کارشناسان آمار | پژوهشگران پیمایشی و افکارسنجی | دستیاران آموزشی در آموزش عالی | نویسندگان متون فنی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | جغرافیا | مدیریت و امور اداری | ریاضیات | آموزش و تدریس | زیست‌شناسی | مکانیک | رایانه و الکترونیک | امور اداری و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | جغرافیا | مدیریت و اداره | ریاضیات | آموزش و پرورش | زیست‌شناسی | مکانیک | رایانه و الکترونیک | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | دید دور | دید نزدیک | تجسم فضایی | چابکی دستی | پایداری دست و بازو | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | تشخیص گفتار | بیان کتبی | ابتکار و اصالت | تمایز رنگ‌ها | قدرت تنه | قدرت ایستا | هماهنگی اندام‌ها | دقت کنترل | چابکی انگشتان</t>
+          <t>ترتیب‌دهی اطلاعات | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | بینایی دور | بینایی نزدیک | تجسم | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | بیان کتبی | اصالت | تشخیص رنگ بصری | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت منابع طبیعی | بازرسان نظارت و انطباق محیط‌زیست | کاردان‌ها و تکنسین‌های مهندسی محیط‌زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | کارشناسان و دانشمندان علوم محیط‌زیست ازجمله بهداشت محیط | سرپرستان رده‌اول کارگران کشاورزی، صیادی و جنگل‌داری | سرپرستان رده‌اول کارگران فضای سبز و باغبانی | بازرسان و کارشناسان پیشگیری و اطفای حریق جنگل | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان و مهندسان جنگل‌داری | تکنسین‌های آب‌شناسی و هیدرولوژی | اکولوژیست‌های صنعتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌های کشاورزی دقیق | کارشناسان مدیریت مرتع و آبخیز | کارشناسان و متخصصان خاک و گیاه | متخصصان منابع آب</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت از منابع طبیعی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | بازرسان و کارشناسان پیشگیری از حریق جنگل | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | تکنسین‌های آب‌شناسی و هیدرولوژی | بوم‌شناسان صنعتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌های کشاورزی دقیق | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | ایمنی و امنیت عمومی | آموزش و تدریس | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | شیمی | اداری | زیست‌شناسی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | آموزش و پرورش | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره | شیمی | اداری | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | انعطاف‌پذیری بستار | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید دور | تشخیص گفتار | وضوح گفتار | تمایز رنگ‌ها | سرعت ادراک | روانی و سیالی ایده‌ها | سرعت بستار | تجسم فضایی | پایداری دست و بازو | توجه انتخابی</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | انعطاف‌پذیری بستار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی دور | تشخیص گفتار | وضوح گفتار | تشخیص رنگ بصری | سرعت ادراکی | روانی ایده‌ها | سرعت بستار | تجسم | ثبات دست و بازو | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | بازرسان مرگ مشکوک و کارشناسان پزشکی قانونی | تکنسین‌های سیتوژنتیک | دانشمندان داده | کارآگاهان و بازرسان کشف جرم | تحلیل‌گران جرایم دیجیتال و فارنزیک رایانه‌ای | بازرسان نظارت و انطباق محیط‌زیست | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | بازرسان و تحلیل‌گران تقلب و جعل | تکنسین‌های بافت‌شناسی | تحلیل‌گران اطلاعاتی و امنیتی | کاردان‌ها و تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان آزمایشگاه‌های تشخیص پزشکی و بالینی | میکروبیولوژیست‌ها | تکنسین‌های پایش و حفاظت پرتوی | متخصصان آزمون نفوذپذیری و امنیت سایبری | خون‌گیرها و فلبوتومیست‌ها | پزشکان متخصص آسیب‌شناسی (پاتولوژیست) | افسران تشخیص هویت و ثبت سوابق پلیس | کارآگاهان و محققان خصوصی</t>
+          <t>تکنسین‌های علوم زیستی | پزشکان قانونی و بازرسان مرگ مشکوک | کارشناسان سیتوژنتیک | دانشمندان داده | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | بازرسان رعایت ضوابط زیست‌محیطی | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان بازرسی، کشف و تحلیل تقلب | کاردان‌های پاتولوژی و بافت‌شناسی | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | تکنسین‌های پایش و حفاظت پرتوی | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان و تکنسین‌های خون‌گیری | پزشکان متخصص پاتولوژی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | کارآگاهان و بازرسان خصوصی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | پایداری دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل | هماهنگی اندام‌ها | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | تکنسین‌های شیمی | تکنسین‌های کشاورزی | تکنسین‌های علوم و صنایع غذایی | تکنسین‌های علوم و حفاظت محیط‌زیست ازجمله بهداشت محیط | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های آب‌شناسی و هیدرولوژی | تکنسین‌های هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | کارشناسان تحلیل کنترل کیفیت | تکنسین‌های سنجش از دور | تکنسین‌های کشاورزی دقیق | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های کالیبراسیون | زیست‌شناسان | شیمیدانان</t>
+          <t>تکنسین‌های علوم زیستی | تکنسین‌های شیمی | تکنسین‌های کشاورزی | تکنسین‌های علوم و صنایع غذایی | تکنسین‌های علوم و بهداشت محیط زیست | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های آب‌شناسی و هیدرولوژی | تکنسین‌های هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | کارشناسان تحلیل کنترل کیفیت | تکنسین‌های سنجش از دور | تکنسین‌های کشاورزی دقیق | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌ها و کارشناسان فنی کالیبراسیون | زیست‌شناسان | شیمی‌دانان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | نظارت | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید دور | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستار | استدلال ریاضی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | چابکی انگشتان | پایداری دست و بازو</t>
+          <t>بینایی نزدیک | درک کتبی | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی دور | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | کاردان‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های شیمی | شیمیدانان | تکنسین‌های علوم و صنایع غذایی | مهندسان ایمنی و بهداشت به‌جز مهندسان و بازرسان ایمنی معدن | متخصصان بافت‌شناسی آزمایشگاهی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | بازرسان، آزمون‌گران، درجه‌بندان، نمونه‌برداران و توزین‌کنندگان | کاردان‌ها و تکنسین‌های مهندسی مکانیک | کاردان‌ها و تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان آزمایشگاه‌های تشخیص پزشکی و بالینی | کاردان‌ها و تکنسین‌های مهندسی نانوفناوری | متخصصان آزمون نفوذپذیری و امنیت سایبری | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | کارشناسان آزمون و تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های شیمی | شیمی‌دانان | تکنسین‌های علوم و صنایع غذایی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان و تکنسین‌های مهندسی مکانیک | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات | شنیدن فعال | نظارت | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات | گوش دادن فعال | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | رایانه و الکترونیک | ریاضیات | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی</t>
+          <t>جغرافیا | رایانه و الکترونیک | ریاضیات | خدمات مشتری و شخصی | مهندسی و فناوری | تولید و فرآوری | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | بیان شفاهی | دید نزدیک | استدلال استقرایی | درک شفاهی | بیان کتبی | وضوح گفتار | درک کتبی | انعطاف‌پذیری بستار | تشخیص گفتار | روانی و سیالی ایده‌ها | ابتکار و اصالت | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | تجسم فضایی | توجه انتخابی | سرعت ادراک | مهارت محاسبات عددی</t>
+          <t>استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان شفاهی | بینایی نزدیک | استدلال استقرایی | درک شفاهی | بیان کتبی | وضوح گفتار | درک کتبی | انعطاف‌پذیری بستار | تشخیص گفتار | روانی ایده‌ها | اصالت | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | توجه انتخابی | سرعت ادراکی | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های اویونیک | کاردان‌ها و تکنسین‌های کالیبراسیون | تصویربرداران تلویزیون، ویدئو و سینما | کارتوگراف‌ها و کارشناسان فتوگرامتری | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کاردان‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | نقشه‌برداران ژئودتیک | کاردان‌ها و تکنسین‌های سیستم اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های کشاورزی دقیق | کارشناسان سامانه‌های شناسایی با امواج رادیویی (RFID) | دانشمندان و کارشناسان فناوری سنجش از دور | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | تکنسین‌های نقشه‌برداری و نقشه‌کشی | نقشه‌برداران</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تصویربرداران تلویزیون، ویدیو و سینما | کارشناسان نقشه‌نگاری و فتوگرامتری | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان نقشه‌برداری ژئودزی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های کشاورزی دقیق | متخصصان سامانه‌های شناسایی با امواج رادیویی | دانشمندان و فناوران سنجش از دور | مهندسان رباتیک | تکنسین‌های رباتیک | توسعه‌دهندگان نرم‌افزار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌برداری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
